--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,275 +1009,275 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>190144935.9247468</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-2046777.64</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>96.09</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>35.19</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>27444</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>190243560.7673913</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-3377.16</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.513858044195834</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-32.99704678275921</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-24.83348021878272</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>6.41</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>97.66</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>35.72</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>27890</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,47 +1440,47 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1490,27 +1490,27 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>5043808.52</v>
+        <v>-3377.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,37 +1613,37 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1871,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>12414421.38</v>
+        <v>5043808.52</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,37 +2044,37 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>19289172.38</v>
+        <v>12414421.38</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,37 +2475,37 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5200.448</t>
+          <t>4338.789</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,84 +2617,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-4.48</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>130.65</t>
+          <t>130.23</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>169345246.0</t>
+          <t>138128762.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>177276809.8</t>
+          <t>188080320.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>116403763.6</t>
+          <t>125592083.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>148669973.02</t>
+          <t>149596455.58</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>60873046</t>
+          <t>62488236</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>985109.7795021855</t>
+          <t>3801119.409873142</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>23085739.93</v>
+        <v>19289172.38</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10078.501</t>
+          <t>5200.448</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>130.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>328331279.0</t>
+          <t>169345246.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>154409017.6</t>
+          <t>177276809.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>104687327.4</t>
+          <t>116403763.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148125748.02</t>
+          <t>148669973.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>49721690</t>
+          <t>60873046</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3033186.611268789</t>
+          <t>985109.7795021855</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>24340293.86</v>
+        <v>23085739.93</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,22 +3337,22 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7595.858</t>
+          <t>10078.501</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>47.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.61</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>244481034.0</t>
+          <t>328331279.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>101671732.8</t>
+          <t>154409017.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>75136860.7</t>
+          <t>104687327.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>144052703.68</t>
+          <t>148125748.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>26534872</t>
+          <t>49721690</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8010183.061039831</t>
+          <t>-3033186.611268789</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>8228999.74</v>
+        <v>24340293.86</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1985.981</t>
+          <t>7595.858</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.61</t>
+          <t>-116.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>60115279.0</t>
+          <t>244481034.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>63614706.6</t>
+          <t>101671732.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>54980733.8</t>
+          <t>75136860.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>141082314.24</t>
+          <t>144052703.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8633972</t>
+          <t>26534872</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-10962761.751592</t>
+          <t>-8010183.061039831</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-6097072.75</v>
+        <v>8228999.74</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2787.443</t>
+          <t>1985.981</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,52 +4457,52 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-39.37</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.31</t>
+          <t>-117.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>84111211.0</t>
+          <t>60115279.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>63103847.2</t>
+          <t>63614706.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>55179132.8</t>
+          <t>54980733.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>142104550.16</t>
+          <t>141082314.24</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7924714</t>
+          <t>8633972</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-11847432.4783745</t>
+          <t>-10962761.751592</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-6591664.25</v>
+        <v>-6097072.75</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1805.45</t>
+          <t>2787.443</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-24.62</t>
+          <t>-39.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>55006285.0</t>
+          <t>84111211.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>55530717.4</t>
+          <t>63103847.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>52417035.1</t>
+          <t>55179132.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>143466380.64</t>
+          <t>142104550.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3113682</t>
+          <t>7924714</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12803026.70160364</t>
+          <t>-11847432.4783745</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-9633799.66</v>
+        <v>-6591664.25</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2101.318</t>
+          <t>1805.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,72 +5203,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5.94</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>30.94</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>31.12</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
-      </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.82</t>
+          <t>-24.62</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.80</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190243560.7673913</t>
+          <t>190144935.9247468</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>64644855.0</t>
+          <t>55006285.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>54965637.2</t>
+          <t>55530717.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>52951387.1</t>
+          <t>52417035.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>147090236.96</t>
+          <t>143466380.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2014250</t>
+          <t>3113682</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13379249.79917039</t>
+          <t>-12803026.70160364</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-10517258.2</v>
+        <v>-9633799.66</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.513858044195834</t>
+          <t>-26.84197020242426</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-32.99704678275921</t>
+          <t>-29.45200131802344</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-24.83348021878272</t>
+          <t>-23.99786452462518</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>97.66</t>
+          <t>96.09</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>26104681.15</v>
+        <v>23788810.96</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,27 +5918,27 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5998,27 +5998,27 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.55</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>22884307.44</v>
+        <v>26104681.15</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,22 +6349,22 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6429,27 +6429,27 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-13.52</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,57 +6612,57 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6672,19 +6672,19 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-3637077.54</v>
+        <v>22884307.44</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,42 +6780,42 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6860,27 +6860,27 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-13.4</t>
+          <t>-16.79</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,68 +7022,68 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -7093,27 +7093,27 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-3129592.74</v>
+        <v>-3637077.54</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,42 +7211,42 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7291,27 +7291,27 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1082.717</t>
+          <t>1708.183</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-16.67</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,47 +7474,47 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7524,27 +7524,27 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-82.36</t>
+          <t>-83.07</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>53373801.0</t>
+          <t>83042251.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>69248881.0</t>
+          <t>69130629.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>63355536.9</t>
+          <t>64051334.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>66796358.2</t>
+          <t>67435324.36</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5893344</t>
+          <t>5079294</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1272767.793881224</t>
+          <t>-1558433.170673689</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-4915192.15</v>
+        <v>-3129592.74</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7722,27 +7722,27 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>921.873</t>
+          <t>1082.717</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-15.5</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,210 +7905,210 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>47.96</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>47.01</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-82.36</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>157459326.8063584</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>53373801.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>69248881.0</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>63355536.9</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>66796358.2</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>5893344</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-1272767.793881224</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>-4915192.15</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>56.93007928480538</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>1.579608048120825</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>-12.19938190710867</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>49.23999999999999</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>46.93</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-82.17</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>157325744.9587554</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>45639464.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>65621638.0</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>69613767.7</t>
-        </is>
-      </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>66703346.78</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-3992129</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-610508.8195512352</t>
-        </is>
-      </c>
-      <c r="BC18" t="n">
-        <v>-4111743.38</v>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>9.38</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>30.83277115278292</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-29.82645388064249</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>-11.84424534662142</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8153,27 +8153,27 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2291.505</t>
+          <t>921.873</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-15.73</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,93 +8315,93 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>85.05</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>49.23999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-81.97</t>
+          <t>-82.17</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>113309831.0</t>
+          <t>45639464.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>65379602.8</t>
+          <t>65621638.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>72812641.2</t>
+          <t>69613767.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>66524390.0</t>
+          <t>66703346.78</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-7433038</t>
+          <t>-3992129</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>26079.28150018654</t>
+          <t>-610508.8195512352</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-1988432.47</v>
+        <v>-4111743.38</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,32 +8504,32 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8584,12 +8584,12 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1026.941</t>
+          <t>2291.505</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-14.92</t>
+          <t>-19.06</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.87</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-81.49</t>
+          <t>-81.97</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>50287798.0</t>
+          <t>113309831.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>53195476.0</t>
+          <t>65379602.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>67534318.2</t>
+          <t>72812641.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>65231934.8</t>
+          <t>66524390.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-14338842</t>
+          <t>-7433038</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>392354.144627068</t>
+          <t>26079.28150018654</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-6134512.19</v>
+        <v>-1988432.47</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,42 +8935,42 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9015,27 +9015,27 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1697.481</t>
+          <t>1026.941</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-18.23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.69</t>
+          <t>-21.23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-80.42</t>
+          <t>-81.49</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>83633511.0</t>
+          <t>50287798.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>58972040.2</t>
+          <t>53195476.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>71649974.9</t>
+          <t>67534318.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>65238381.22</t>
+          <t>65231934.8</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-12677934</t>
+          <t>-14338842</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1579057.113704596</t>
+          <t>392354.144627068</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-5086032.81</v>
+        <v>-6134512.19</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9446,27 +9446,27 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>726.674</t>
+          <t>1697.481</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-13.29</t>
+          <t>-17.75</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-39.12</t>
+          <t>-17.69</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,195 +9629,195 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.77</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-80.42</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>157459326.8063584</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>83633511.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>58972040.2</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>71649974.9</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>65238381.22</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-12677934</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>1579057.113704596</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-5086032.81</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>8.39</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-78.83</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>157325744.9587554</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>35237586.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>57462192.8</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>94393531.4</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>65028952.9</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-36931338</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>2790891.645983021</t>
-        </is>
-      </c>
-      <c r="BC22" t="n">
-        <v>-6979316.08</v>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>7.28</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9877,27 +9877,27 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>916.056</t>
+          <t>726.674</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-12.47</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-27.03</t>
+          <t>-39.12</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>30.43</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
           <t>15.22</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>5.07</t>
-        </is>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.26000000000001</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.74</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.57</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-40.59</t>
+          <t>-40.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-76.68</t>
+          <t>-78.83</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157325744.9587554</t>
+          <t>157459326.8063584</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>44429288.0</t>
+          <t>35237586.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>73605897.4</t>
+          <t>57462192.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>100871518.7</t>
+          <t>94393531.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>67313461.9</t>
+          <t>65028952.9</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-27265621</t>
+          <t>-36931338</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>4567293.049891738</t>
+          <t>2790891.645983021</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-4249467.48</v>
+        <v>-6979316.08</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>30.83277115278292</t>
+          <t>56.93007928480538</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-29.82645388064249</t>
+          <t>1.579608048120825</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-11.84424534662142</t>
+          <t>-12.19938190710867</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>28.42</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>31329</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10308,27 +10308,27 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>油電燃氣業平上市</t>
+          <t>油電燃氣業右下上市</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>85549414.4</t>
+          <t>81485371.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>134538953.8</t>
+          <t>133719606.02</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2046777.64</v>
+        <v>-695037.38</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,275 +1440,275 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>190125525.3489884</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-2046777.64</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>6.57</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>95.31</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>34.59</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>27221</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>190144935.9247468</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-3377.16</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>96.09</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>35.19</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>27444</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,47 +1871,47 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1921,27 +1921,27 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>5043808.52</v>
+        <v>-3377.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2302,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>12414421.38</v>
+        <v>5043808.52</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>19289172.38</v>
+        <v>12414421.38</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5200.448</t>
+          <t>4338.789</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,84 +3048,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-2.79</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-6.18</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.87</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>130.65</t>
+          <t>130.23</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>169345246.0</t>
+          <t>138128762.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>177276809.8</t>
+          <t>188080320.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>116403763.6</t>
+          <t>125592083.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>148669973.02</t>
+          <t>149596455.58</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>60873046</t>
+          <t>62488236</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>985109.7795021855</t>
+          <t>3801119.409873142</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>23085739.93</v>
+        <v>19289172.38</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10078.501</t>
+          <t>5200.448</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-7.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>130.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>328331279.0</t>
+          <t>169345246.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>154409017.6</t>
+          <t>177276809.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>104687327.4</t>
+          <t>116403763.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148125748.02</t>
+          <t>148669973.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>49721690</t>
+          <t>60873046</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3033186.611268789</t>
+          <t>985109.7795021855</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>24340293.86</v>
+        <v>23085739.93</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7595.858</t>
+          <t>10078.501</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>47.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.61</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>244481034.0</t>
+          <t>328331279.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>101671732.8</t>
+          <t>154409017.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>75136860.7</t>
+          <t>104687327.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>144052703.68</t>
+          <t>148125748.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>26534872</t>
+          <t>49721690</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8010183.061039831</t>
+          <t>-3033186.611268789</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>8228999.74</v>
+        <v>24340293.86</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1985.981</t>
+          <t>7595.858</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-6.07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.61</t>
+          <t>-116.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>60115279.0</t>
+          <t>244481034.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>63614706.6</t>
+          <t>101671732.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>54980733.8</t>
+          <t>75136860.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>141082314.24</t>
+          <t>144052703.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8633972</t>
+          <t>26534872</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-10962761.751592</t>
+          <t>-8010183.061039831</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-6097072.75</v>
+        <v>8228999.74</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2787.443</t>
+          <t>1985.981</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,52 +4888,52 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -4943,22 +4943,22 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.94</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-39.37</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.31</t>
+          <t>-117.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>84111211.0</t>
+          <t>60115279.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>63103847.2</t>
+          <t>63614706.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>55179132.8</t>
+          <t>54980733.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>142104550.16</t>
+          <t>141082314.24</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7924714</t>
+          <t>8633972</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-11847432.4783745</t>
+          <t>-10962761.751592</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-6591664.25</v>
+        <v>-6097072.75</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,69 +5031,69 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
+          <t>8.53</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
           <t>6.57</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>6.52</t>
-        </is>
-      </c>
       <c r="BT11" t="inlineStr">
         <is>
           <t>23.80</t>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1805.45</t>
+          <t>2787.443</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-24.62</t>
+          <t>-39.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190144935.9247468</t>
+          <t>190125525.3489884</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>55006285.0</t>
+          <t>84111211.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>55530717.4</t>
+          <t>63103847.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>52417035.1</t>
+          <t>55179132.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>143466380.64</t>
+          <t>142104550.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3113682</t>
+          <t>7924714</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12803026.70160364</t>
+          <t>-11847432.4783745</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-9633799.66</v>
+        <v>-6591664.25</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>96.09</t>
+          <t>95.31</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>34.59</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>27221</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>188514316.2</t>
+          <t>211755874.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>82208595.36</t>
+          <t>84907732.44</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>23788810.96</v>
+        <v>24028515.45</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5943,17 +5943,17 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>26104681.15</v>
+        <v>23788810.96</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-6.72</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>22884307.44</v>
+        <v>26104681.15</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-16.79</t>
+          <t>-11.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,57 +7043,57 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7103,19 +7103,19 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-3637077.54</v>
+        <v>22884307.44</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-16.67</t>
+          <t>-21.14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,68 +7453,68 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7524,27 +7524,27 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-3129592.74</v>
+        <v>-3637077.54</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1082.717</t>
+          <t>1708.183</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,47 +7905,47 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -7955,27 +7955,27 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-82.36</t>
+          <t>-83.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>53373801.0</t>
+          <t>83042251.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>69248881.0</t>
+          <t>69130629.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>63355536.9</t>
+          <t>64051334.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>66796358.2</t>
+          <t>67435324.36</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5893344</t>
+          <t>5079294</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1272767.793881224</t>
+          <t>-1558433.170673689</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-4915192.15</v>
+        <v>-3129592.74</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>921.873</t>
+          <t>1082.717</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-22.76</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,210 +8336,210 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>47.96</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>47.01</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-82.36</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>157663389.9155844</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>53373801.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>69248881.0</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>63355536.9</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>66796358.2</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>5893344</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-1272767.793881224</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-4915192.15</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>56.93007928480538</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>1.579608048120825</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-12.19938190710867</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>49.23999999999999</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>46.93</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-82.17</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>157459326.8063584</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>45639464.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>65621638.0</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>69613767.7</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>66703346.78</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-3992129</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-610508.8195512352</t>
-        </is>
-      </c>
-      <c r="BC19" t="n">
-        <v>-4111743.38</v>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>9.38</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>56.93007928480538</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>1.579608048120825</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>-12.19938190710867</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2291.505</t>
+          <t>921.873</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-19.06</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,93 +8746,93 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>85.05</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>49.23999999999999</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-81.97</t>
+          <t>-82.17</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>113309831.0</t>
+          <t>45639464.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>65379602.8</t>
+          <t>65621638.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>72812641.2</t>
+          <t>69613767.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>66524390.0</t>
+          <t>66703346.78</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-7433038</t>
+          <t>-3992129</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>26079.28150018654</t>
+          <t>-610508.8195512352</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-1988432.47</v>
+        <v>-4111743.38</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1026.941</t>
+          <t>2291.505</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-18.23</t>
+          <t>-23.51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-81.49</t>
+          <t>-81.97</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>50287798.0</t>
+          <t>113309831.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>53195476.0</t>
+          <t>65379602.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>67534318.2</t>
+          <t>72812641.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>65231934.8</t>
+          <t>66524390.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-14338842</t>
+          <t>-7433038</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>392354.144627068</t>
+          <t>26079.28150018654</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6134512.19</v>
+        <v>-1988432.47</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1697.481</t>
+          <t>1026.941</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-17.75</t>
+          <t>-22.64</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.69</t>
+          <t>-21.23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-80.42</t>
+          <t>-81.49</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>83633511.0</t>
+          <t>50287798.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>58972040.2</t>
+          <t>53195476.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>71649974.9</t>
+          <t>67534318.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>65238381.22</t>
+          <t>65231934.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-12677934</t>
+          <t>-14338842</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1579057.113704596</t>
+          <t>392354.144627068</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-5086032.81</v>
+        <v>-6134512.19</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>726.674</t>
+          <t>1697.481</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.55</t>
+          <t>-22.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-39.12</t>
+          <t>-17.69</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>32.61</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>48.82</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.77</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>46.57</t>
+          <t>46.66</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-40.56</t>
+          <t>-32.58</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-78.83</t>
+          <t>-80.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157459326.8063584</t>
+          <t>157663389.9155844</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>35237586.0</t>
+          <t>83633511.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>57462192.8</t>
+          <t>58972040.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>94393531.4</t>
+          <t>71649974.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>65028952.9</t>
+          <t>65238381.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-36931338</t>
+          <t>-12677934</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>2790891.645983021</t>
+          <t>1579057.113704596</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6979316.08</v>
+        <v>-5086032.81</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>29357</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>48.95</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,69 +893,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>81485371.0</t>
+          <t>78008957.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>133719606.02</t>
+          <t>132601320.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-695037.38</v>
+        <v>-3246006.49</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>85549414.4</t>
+          <t>81485371.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>134538953.8</t>
+          <t>133719606.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2046777.64</v>
+        <v>-695037.38</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,275 +1871,275 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>190004740.3961039</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-2046777.64</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>6.55</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>95.63</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>34.54</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>27310</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>190125525.3489884</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-3377.16</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>6.57</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>95.31</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>34.59</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>27221</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,47 +2302,47 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2352,27 +2352,27 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>5043808.52</v>
+        <v>-3377.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>12414421.38</v>
+        <v>5043808.52</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>19289172.38</v>
+        <v>12414421.38</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5200.448</t>
+          <t>4338.789</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,84 +3479,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.45</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-7.05</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>130.65</t>
+          <t>130.23</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>169345246.0</t>
+          <t>138128762.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>177276809.8</t>
+          <t>188080320.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>116403763.6</t>
+          <t>125592083.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>148669973.02</t>
+          <t>149596455.58</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>60873046</t>
+          <t>62488236</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>985109.7795021855</t>
+          <t>3801119.409873142</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>23085739.93</v>
+        <v>19289172.38</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10078.501</t>
+          <t>5200.448</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>130.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>328331279.0</t>
+          <t>169345246.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>154409017.6</t>
+          <t>177276809.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>104687327.4</t>
+          <t>116403763.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148125748.02</t>
+          <t>148669973.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>49721690</t>
+          <t>60873046</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3033186.611268789</t>
+          <t>985109.7795021855</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>24340293.86</v>
+        <v>23085739.93</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7595.858</t>
+          <t>10078.501</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>47.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.61</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>244481034.0</t>
+          <t>328331279.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>101671732.8</t>
+          <t>154409017.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>75136860.7</t>
+          <t>104687327.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>144052703.68</t>
+          <t>148125748.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>26534872</t>
+          <t>49721690</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8010183.061039831</t>
+          <t>-3033186.611268789</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>8228999.74</v>
+        <v>24340293.86</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1985.981</t>
+          <t>7595.858</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-5.72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.61</t>
+          <t>-116.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>60115279.0</t>
+          <t>244481034.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>63614706.6</t>
+          <t>101671732.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>54980733.8</t>
+          <t>75136860.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>141082314.24</t>
+          <t>144052703.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8633972</t>
+          <t>26534872</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-10962761.751592</t>
+          <t>-8010183.061039831</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-6097072.75</v>
+        <v>8228999.74</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2787.443</t>
+          <t>1985.981</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>15.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,52 +5319,52 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5374,22 +5374,22 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.94</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-39.37</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.31</t>
+          <t>-117.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190125525.3489884</t>
+          <t>190004740.3961039</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>84111211.0</t>
+          <t>60115279.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>63103847.2</t>
+          <t>63614706.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>55179132.8</t>
+          <t>54980733.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>142104550.16</t>
+          <t>141082314.24</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7924714</t>
+          <t>8633972</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-11847432.4783745</t>
+          <t>-10962761.751592</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6591664.25</v>
+        <v>-6097072.75</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>95.31</t>
+          <t>95.63</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27310</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>211755874.2</t>
+          <t>216518198.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>84907732.44</t>
+          <t>85485799.7</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>24028515.45</v>
+        <v>14830238.84</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>188514316.2</t>
+          <t>211755874.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>82208595.36</t>
+          <t>84907732.44</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>23788810.96</v>
+        <v>24028515.45</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>26104681.15</v>
+        <v>23788810.96</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-11.57</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>22884307.44</v>
+        <v>26104681.15</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-21.14</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,57 +7474,57 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-3637077.54</v>
+        <v>22884307.44</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-18.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,68 +7884,68 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -7955,27 +7955,27 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-3129592.74</v>
+        <v>-3637077.54</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1082.717</t>
+          <t>1708.183</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-22.76</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,47 +8336,47 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -8386,27 +8386,27 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-82.36</t>
+          <t>-83.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>53373801.0</t>
+          <t>83042251.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>69248881.0</t>
+          <t>69130629.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>63355536.9</t>
+          <t>64051334.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>66796358.2</t>
+          <t>67435324.36</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5893344</t>
+          <t>5079294</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1272767.793881224</t>
+          <t>-1558433.170673689</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-4915192.15</v>
+        <v>-3129592.74</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>921.873</t>
+          <t>1082.717</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,210 +8767,210 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>47.96</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>47.01</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-82.36</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>157614261.0021614</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>53373801.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>69248881.0</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>63355536.9</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>66796358.2</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>5893344</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-1272767.793881224</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-4915192.15</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>56.93007928480538</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>1.579608048120825</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>-12.19938190710867</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>49.23999999999999</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>46.93</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-82.17</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>157663389.9155844</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>45639464.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>65621638.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>69613767.7</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>66703346.78</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>-3992129</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-610508.8195512352</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>-4111743.38</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>9.38</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>56.93007928480538</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>1.579608048120825</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>-12.19938190710867</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2291.505</t>
+          <t>921.873</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-23.51</t>
+          <t>-20.56</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,93 +9177,93 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>85.05</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>49.23999999999999</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-81.97</t>
+          <t>-82.17</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>113309831.0</t>
+          <t>45639464.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>65379602.8</t>
+          <t>65621638.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>72812641.2</t>
+          <t>69613767.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>66524390.0</t>
+          <t>66703346.78</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-7433038</t>
+          <t>-3992129</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>26079.28150018654</t>
+          <t>-610508.8195512352</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-1988432.47</v>
+        <v>-4111743.38</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1026.941</t>
+          <t>2291.505</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-22.64</t>
+          <t>-20.8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.87</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-81.49</t>
+          <t>-81.97</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>50287798.0</t>
+          <t>113309831.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>53195476.0</t>
+          <t>65379602.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>67534318.2</t>
+          <t>72812641.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>65231934.8</t>
+          <t>66524390.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-14338842</t>
+          <t>-7433038</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>392354.144627068</t>
+          <t>26079.28150018654</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6134512.19</v>
+        <v>-1988432.47</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1697.481</t>
+          <t>1026.941</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-22.14</t>
+          <t>-19.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.69</t>
+          <t>-21.23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>11.22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>60.87</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>47.81</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-32.58</t>
+          <t>-23.10</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-80.42</t>
+          <t>-81.49</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157663389.9155844</t>
+          <t>157614261.0021614</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>83633511.0</t>
+          <t>50287798.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>58972040.2</t>
+          <t>53195476.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>71649974.9</t>
+          <t>67534318.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>65238381.22</t>
+          <t>65231934.8</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-12677934</t>
+          <t>-14338842</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1579057.113704596</t>
+          <t>392354.144627068</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-5086032.81</v>
+        <v>-6134512.19</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>48.95</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>78008957.4</t>
+          <t>76714098.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>132601320.34</t>
+          <t>127513369.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-3246006.49</v>
+        <v>-6380378.21</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,94 +1324,94 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>32.65</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>-3.37</t>
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>81485371.0</t>
+          <t>78008957.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>133719606.02</t>
+          <t>132601320.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-695037.38</v>
+        <v>-3246006.49</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>85549414.4</t>
+          <t>81485371.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>134538953.8</t>
+          <t>133719606.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-2046777.64</v>
+        <v>-695037.38</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,275 +2302,275 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>189843097.6621037</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-2046777.64</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>6.45</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>97.03</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>34.7</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>27712</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>190004740.3961039</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-3377.16</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>6.55</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>95.63</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>34.54</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>27310</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>5043808.52</v>
+        <v>-3377.16</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,67 +3164,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>12414421.38</v>
+        <v>5043808.52</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>19289172.38</v>
+        <v>12414421.38</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5200.448</t>
+          <t>4338.789</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,84 +3910,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-6.7</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>98.58</t>
+          <t>82.23</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>130.65</t>
+          <t>130.23</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.76</t>
+          <t>-108.12</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>169345246.0</t>
+          <t>138128762.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>177276809.8</t>
+          <t>188080320.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>116403763.6</t>
+          <t>125592083.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>148669973.02</t>
+          <t>149596455.58</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>60873046</t>
+          <t>62488236</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>985109.7795021855</t>
+          <t>3801119.409873142</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>23085739.93</v>
+        <v>19289172.38</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10078.501</t>
+          <t>5200.448</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>130.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>328331279.0</t>
+          <t>169345246.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>154409017.6</t>
+          <t>177276809.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>104687327.4</t>
+          <t>116403763.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>148125748.02</t>
+          <t>148669973.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>49721690</t>
+          <t>60873046</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3033186.611268789</t>
+          <t>985109.7795021855</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>24340293.86</v>
+        <v>23085739.93</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7595.858</t>
+          <t>10078.501</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.72</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>47.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>11.07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.74</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>31.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>65.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.61</t>
+          <t>-114.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>244481034.0</t>
+          <t>328331279.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>101671732.8</t>
+          <t>154409017.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>75136860.7</t>
+          <t>104687327.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>144052703.68</t>
+          <t>148125748.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>26534872</t>
+          <t>49721690</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8010183.061039831</t>
+          <t>-3033186.611268789</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>8228999.74</v>
+        <v>24340293.86</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>14.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1985.981</t>
+          <t>7595.858</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.70</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>1669</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.61</t>
+          <t>-116.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190004740.3961039</t>
+          <t>189843097.6621037</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>60115279.0</t>
+          <t>244481034.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>63614706.6</t>
+          <t>101671732.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>54980733.8</t>
+          <t>75136860.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>141082314.24</t>
+          <t>144052703.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8633972</t>
+          <t>26534872</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-10962761.751592</t>
+          <t>-8010183.061039831</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6097072.75</v>
+        <v>8228999.74</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>95.63</t>
+          <t>97.03</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27712</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>216518198.4</t>
+          <t>146516831.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>85485799.7</t>
+          <t>86052402.7</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>14830238.84</v>
+        <v>6770002.29</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>211755874.2</t>
+          <t>216518198.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>84907732.44</t>
+          <t>85485799.7</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>24028515.45</v>
+        <v>14830238.84</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>188514316.2</t>
+          <t>211755874.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>82208595.36</t>
+          <t>84907732.44</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>23788810.96</v>
+        <v>24028515.45</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>26104681.15</v>
+        <v>23788810.96</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>22884307.44</v>
+        <v>26104681.15</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,57 +7905,57 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,19 +7965,19 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-3637077.54</v>
+        <v>22884307.44</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-17.78</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,68 +8315,68 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -8386,27 +8386,27 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-3129592.74</v>
+        <v>-3637077.54</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1082.717</t>
+          <t>1708.183</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-17.65</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,47 +8767,47 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -8817,27 +8817,27 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-82.36</t>
+          <t>-83.07</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>53373801.0</t>
+          <t>83042251.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>69248881.0</t>
+          <t>69130629.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>63355536.9</t>
+          <t>64051334.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>66796358.2</t>
+          <t>67435324.36</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>5893344</t>
+          <t>5079294</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1272767.793881224</t>
+          <t>-1558433.170673689</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-4915192.15</v>
+        <v>-3129592.74</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>921.873</t>
+          <t>1082.717</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-20.56</t>
+          <t>-19.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,210 +9198,210 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>47.96</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>47.01</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-82.36</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>157529282.4755396</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>53373801.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>69248881.0</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>63355536.9</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>66796358.2</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>5893344</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-1272767.793881224</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-4915192.15</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>56.93007928480538</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>1.579608048120825</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-12.19938190710867</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>49.23999999999999</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>46.93</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-82.17</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>157614261.0021614</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>45639464.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>65621638.0</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>69613767.7</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>66703346.78</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>-3992129</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-610508.8195512352</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>-4111743.38</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>9.38</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>56.93007928480538</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>1.579608048120825</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-12.19938190710867</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2291.505</t>
+          <t>921.873</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.8</t>
+          <t>-19.83</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,93 +9608,93 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.29</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>85.05</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>49.23999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>49.04</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-81.97</t>
+          <t>-82.17</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>113309831.0</t>
+          <t>45639464.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>65379602.8</t>
+          <t>65621638.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>72812641.2</t>
+          <t>69613767.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>66524390.0</t>
+          <t>66703346.78</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-7433038</t>
+          <t>-3992129</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>26079.28150018654</t>
+          <t>-610508.8195512352</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-1988432.47</v>
+        <v>-4111743.38</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1026.941</t>
+          <t>2291.505</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-19.95</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-5.32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>60.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>47.81</t>
+          <t>47.87</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-23.10</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-81.49</t>
+          <t>-81.97</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157614261.0021614</t>
+          <t>157529282.4755396</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>50287798.0</t>
+          <t>113309831.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>53195476.0</t>
+          <t>65379602.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>67534318.2</t>
+          <t>72812641.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>65231934.8</t>
+          <t>66524390.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-14338842</t>
+          <t>-7433038</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>392354.144627068</t>
+          <t>26079.28150018654</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6134512.19</v>
+        <v>-1988432.47</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,215 +1014,215 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>31.24</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>189842971.2327586</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>98740967.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>104398068.18</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>160381912</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>13.68</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>31.21</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>189769978.5755396</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>82943757.4</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>110958961.04</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>92683555</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>76714098.8</t>
+          <t>82943757.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>127513369.12</t>
+          <t>110958961.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>51883122</v>
+        <v>92683555</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,67 +1886,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>78008957.4</t>
+          <t>76714098.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>132601320.34</t>
+          <t>127513369.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>70947702</v>
+        <v>51883122</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,69 +2206,69 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>81485371.0</t>
+          <t>78008957.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>133719606.02</t>
+          <t>132601320.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>117808545</v>
+        <v>70947702</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>85549414.4</t>
+          <t>81485371.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>134538953.8</t>
+          <t>133719606.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>81395863</v>
+        <v>117808545</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,280 +3194,280 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>189842971.2327586</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-2046777.640298501</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>81395863</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>35.13</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>28560</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>189769978.5755396</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-3377.162995308638</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>61535262</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.39</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>97.97</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>34.73</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>27980</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,47 +3630,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3680,27 +3680,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5043808.524687648</t>
+          <t>-3377.162995308638</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>58357415</v>
+        <v>61535262</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,67 +4066,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>12414421.38121018</t>
+          <t>5043808.524687648</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>88329770</v>
+        <v>58357415</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>19289172.3769134</t>
+          <t>12414421.38121018</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>138128762</v>
+        <v>88329770</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5200.448</t>
+          <t>4338.789</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,84 +4822,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-4.15</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.79</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,227 +4938,227 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>50.94</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>82.23</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>31.83</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>31.18</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>31.23</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>130.23</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-108.12</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>189842971.2327586</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>138128762.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>188080320.0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>125592083.6</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>149596455.58</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>62488236</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>3801119.409873142</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>19289172.3769134</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>138128762</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>11.37</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>98.58</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>31.56</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>31.14</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>31.17</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>130.65</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-110.76</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>189769978.5755396</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>169345246.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>177276809.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>116403763.6</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>148669973.02</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>60873046</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>985109.7795021855</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>23085739.92874254</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>169345246</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>15.99</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>6.39</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>97.97</t>
-        </is>
-      </c>
       <c r="BW11" t="inlineStr">
         <is>
           <t>9.28%</t>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10078.501</t>
+          <t>5200.448</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>52.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>98.58</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>31.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>65.22</t>
+          <t>130.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.28</t>
+          <t>-110.76</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>189769978.5755396</t>
+          <t>189842971.2327586</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>328331279.0</t>
+          <t>169345246.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>154409017.6</t>
+          <t>177276809.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>104687327.4</t>
+          <t>116403763.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>148125748.02</t>
+          <t>148669973.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>49721690</t>
+          <t>60873046</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3033186.611268789</t>
+          <t>985109.7795021855</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>24340293.86247194</t>
+          <t>23085739.92874254</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>328331279</v>
+        <v>169345246</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>14.56</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>97.97</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>27980</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>111884228.6</t>
+          <t>89118941.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>83731647.22</t>
+          <t>83437284.84</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>45580107</v>
+        <v>52683153</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6078,12 +6078,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.28</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>146516831.0</t>
+          <t>111884228.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>86052402.7</t>
+          <t>83731647.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>65702790</v>
+        <v>45580107</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>216518198.4</t>
+          <t>146516831.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>85485799.7</t>
+          <t>86052402.7</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>82378616</v>
+        <v>65702790</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>211755874.2</t>
+          <t>216518198.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>84907732.44</t>
+          <t>85485799.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>199250041</v>
+        <v>82378616</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>188514316.2</t>
+          <t>211755874.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>82208595.36</t>
+          <t>84907732.44</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>166509589</v>
+        <v>199250041</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7752,17 +7752,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>218743119</v>
+        <v>166509589</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.12</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>415709627</v>
+        <v>218743119</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8624,17 +8624,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-18.49</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,57 +8862,57 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -8922,19 +8922,19 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3637077.537691697</t>
+          <t>22884307.44448899</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>58566995</v>
+        <v>415709627</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-18.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,68 +9277,68 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9348,27 +9348,27 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3129592.743032247</t>
+          <t>-3637077.537691697</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>83042251</v>
+        <v>58566995</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1082.717</t>
+          <t>1708.183</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-18.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,47 +9734,47 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9784,27 +9784,27 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-82.36</t>
+          <t>-83.07</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157401180.2887931</t>
+          <t>157288732.0093257</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>53373801.0</t>
+          <t>83042251.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>69248881.0</t>
+          <t>69130629.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>63355536.9</t>
+          <t>64051334.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>66796358.2</t>
+          <t>67435324.36</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5893344</t>
+          <t>5079294</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1272767.793881224</t>
+          <t>-1558433.170673689</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-4915192.152696162</t>
+          <t>-3129592.743032247</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>53373801</v>
+        <v>83042251</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>921.873</t>
+          <t>1082.717</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-20.56</t>
+          <t>-19.78</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,215 +10170,215 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>94.29</t>
+          <t>82.86</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>92.38</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>49.39</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>49.1</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>47.96</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>47.01</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-4.33</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>0.40</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-82.36</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/10/01</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>157288732.0093257</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>53373801.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>69248881.0</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>63355536.9</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>66796358.2</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>5893344</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-1272767.793881224</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-4915192.152696162</t>
+        </is>
+      </c>
+      <c r="BD23" t="n">
+        <v>53373801</v>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>45.3</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>8.94</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>台汽電</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>油電燃氣業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>56.93007928480538</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>1.579608048120825</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>-12.19938190710867</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>49.23999999999999</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.04</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>46.93</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-82.17</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/10/01</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>157401180.2887931</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>45639464.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>65621638.0</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>69613767.7</t>
-        </is>
-      </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>66703346.78</t>
-        </is>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-3992129</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-610508.8195512352</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-4111743.375334054</t>
-        </is>
-      </c>
-      <c r="BD23" t="n">
-        <v>45639464</v>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>9.38</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>56.93007928480538</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>1.579608048120825</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>-12.19938190710867</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.24</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.85</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.24</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>98740967.2</t>
+          <t>90018253.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>104398068.18</t>
+          <t>101483765.1</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>160381912</v>
+        <v>74194978</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,212 +1450,212 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>31.24</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>189730273.2352941</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>98740967.2</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>104398068.18</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>160381912</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>13.68</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>31.21</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>189842971.2327586</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>82943757.4</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>110958961.04</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>92683555</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
           <t>6.26</t>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>76714098.8</t>
+          <t>82943757.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>127513369.12</t>
+          <t>110958961.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>51883122</v>
+        <v>92683555</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,67 +2322,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>78008957.4</t>
+          <t>76714098.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>132601320.34</t>
+          <t>127513369.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>70947702</v>
+        <v>51883122</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,69 +2642,69 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4.37</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.69</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>81485371.0</t>
+          <t>78008957.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>133719606.02</t>
+          <t>132601320.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>117808545</v>
+        <v>70947702</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>85549414.4</t>
+          <t>81485371.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>134538953.8</t>
+          <t>133719606.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>81395863</v>
+        <v>117808545</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,280 +3630,280 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>189730273.2352941</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-2046777.640298501</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>81395863</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>35.26</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>28560</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>189842971.2327586</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-3377.162995308638</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>61535262</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>35.13</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>28560</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4116,27 +4116,27 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5043808.524687648</t>
+          <t>-3377.162995308638</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>58357415</v>
+        <v>61535262</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,67 +4502,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>12414421.38121018</t>
+          <t>5043808.524687648</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>88329770</v>
+        <v>58357415</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>189842971.2327586</t>
+          <t>189730273.2352941</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>19289172.3769134</t>
+          <t>12414421.38121018</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>138128762</v>
+        <v>88329770</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5200.448</t>
+          <t>4338.789</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,84 +5258,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>31.35</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>49.75</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.28</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>52.29</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-4.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,227 +5374,227 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>50.94</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>82.23</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>31.83</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>31.18</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>31.23</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>130.23</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-108.12</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>189730273.2352941</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>138128762.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>188080320.0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>125592083.6</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>149596455.58</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>62488236</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>3801119.409873142</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>19289172.3769134</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>138128762</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>11.37</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>98.58</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-2.14</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>31.56</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>31.14</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>31.17</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>130.65</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-110.76</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>189842971.2327586</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>169345246.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>177276809.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>116403763.6</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>148669973.02</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>60873046</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>985109.7795021855</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>23085739.92874254</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>169345246</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>15.99</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="BW12" t="inlineStr">
         <is>
           <t>9.28%</t>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>89118941.4</t>
+          <t>56607545.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>83437284.84</t>
+          <t>82624485.32</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>52683153</v>
+        <v>36693061</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>111884228.6</t>
+          <t>89118941.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>83731647.22</t>
+          <t>83437284.84</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>45580107</v>
+        <v>52683153</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.28</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>146516831.0</t>
+          <t>111884228.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>86052402.7</t>
+          <t>83731647.22</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>65702790</v>
+        <v>45580107</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>216518198.4</t>
+          <t>146516831.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>85485799.7</t>
+          <t>86052402.7</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>82378616</v>
+        <v>65702790</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>211755874.2</t>
+          <t>216518198.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>84907732.44</t>
+          <t>85485799.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>199250041</v>
+        <v>82378616</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>188514316.2</t>
+          <t>211755874.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>82208595.36</t>
+          <t>84907732.44</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>166509589</v>
+        <v>199250041</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8188,17 +8188,17 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.13</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>218743119</v>
+        <v>166509589</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>415709627</v>
+        <v>218743119</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9060,17 +9060,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-18.2</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,57 +9298,57 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9358,19 +9358,19 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3637077.537691697</t>
+          <t>22884307.44448899</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>58566995</v>
+        <v>415709627</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-18.08</t>
+          <t>-18.78</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,68 +9713,68 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9784,27 +9784,27 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3129592.743032247</t>
+          <t>-3637077.537691697</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>83042251</v>
+        <v>58566995</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1082.717</t>
+          <t>1708.183</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-19.78</t>
+          <t>-18.66</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.30</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,47 +10170,47 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>895</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>82.86</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>92.38</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.39</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -10220,27 +10220,27 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-16.71</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-82.36</t>
+          <t>-83.07</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157288732.0093257</t>
+          <t>157142243.269341</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>53373801.0</t>
+          <t>83042251.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>69248881.0</t>
+          <t>69130629.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>63355536.9</t>
+          <t>64051334.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>66796358.2</t>
+          <t>67435324.36</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5893344</t>
+          <t>5079294</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1272767.793881224</t>
+          <t>-1558433.170673689</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-4915192.152696162</t>
+          <t>-3129592.743032247</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>53373801</v>
+        <v>83042251</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.24</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>13021.446</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>33.55</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2321.952</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.27</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>5869.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-99.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>90018253.8</t>
+          <t>163075735.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>85751812.4</t>
+          <t>120542346.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>101483765.1</t>
+          <t>106027794.62</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4266441</t>
+          <t>42533388</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-453954.409459276</t>
+          <t>3279487.95126148</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1753824.401134402</t>
+          <t>23813420.93522564</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>74194978</v>
+        <v>436235108</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.24</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>98740967.2</t>
+          <t>90018253.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>104398068.18</t>
+          <t>101483765.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>160381912</v>
+        <v>74194978</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,215 +1886,215 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>31.24</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>190395921.3567335</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>98740967.2</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>104398068.18</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>160381912</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>13.68</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>31.21</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>189730273.2352941</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>82943757.4</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>110958961.04</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>92683555</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.73</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>76714098.8</t>
+          <t>82943757.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>127513369.12</t>
+          <t>110958961.04</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>51883122</v>
+        <v>92683555</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,67 +2758,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.73</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>78008957.4</t>
+          <t>76714098.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>132601320.34</t>
+          <t>127513369.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>70947702</v>
+        <v>51883122</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,69 +3078,69 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8.79</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.69</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>81485371.0</t>
+          <t>78008957.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>133719606.02</t>
+          <t>132601320.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>117808545</v>
+        <v>70947702</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>85549414.4</t>
+          <t>81485371.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>134538953.8</t>
+          <t>133719606.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>81395863</v>
+        <v>117808545</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,280 +4066,280 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>31.82</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>31.44</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>40.91</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-101.85</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>190395921.3567335</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>85549414.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>131413112.1</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>134538953.8</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-45863697</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>3345859.856864722</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-2046777.640298501</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>81395863</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>9.24</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>5.97</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>104.84</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>35.91</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>29943</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>31.3</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>261.70</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-102.04</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>189730273.2352941</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>61535262.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>128774154.3</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-25634863</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>4326339.40180349</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-3377.162995308638</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>61535262</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>11.01</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>28560</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>156498494.4</t>
+          <t>103139291.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>141953833.54</t>
+          <t>137249141.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5043808.524687648</t>
+          <t>-3377.162995308638</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>58357415</v>
+        <v>61535262</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>5.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>193723218.2</t>
+          <t>156498494.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>147438804.66</t>
+          <t>141953833.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>12414421.38121018</t>
+          <t>5043808.524687648</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>88329770</v>
+        <v>58357415</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4338.789</t>
+          <t>2767.799</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>50.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.30</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>82.23</t>
+          <t>74.21</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>130.23</t>
+          <t>187.70</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.12</t>
+          <t>-105.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>189730273.2352941</t>
+          <t>190395921.3567335</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>138128762.0</t>
+          <t>88329770.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>188080320.0</t>
+          <t>193723218.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>125592083.6</t>
+          <t>128668962.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>149596455.58</t>
+          <t>147438804.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>62488236</t>
+          <t>65054255</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3801119.409873142</t>
+          <t>5126242.79007884</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>19289172.3769134</t>
+          <t>12414421.38121018</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>138128762</v>
+        <v>88329770</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>13.32</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>104.84</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>32.85</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.87</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>56607545.4</t>
+          <t>46398517.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>82624485.32</t>
+          <t>82367727.08</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>36693061</v>
+        <v>31333478</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>89118941.4</t>
+          <t>56607545.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>83437284.84</t>
+          <t>82624485.32</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>52683153</v>
+        <v>36693061</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,102 +6576,102 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-35.80</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>47.8</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>48.15</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>48.55</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-14.43</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13.99</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
           <t>-0.24</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-2.88</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-19.44</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>48.15</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>-14.64</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12.08</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-0.97</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>45.99</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>47.28</t>
+          <t>47.13</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>111884228.6</t>
+          <t>89118941.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>83731647.22</t>
+          <t>83437284.84</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>45580107</v>
+        <v>52683153</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6950,12 +6950,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>46.37</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>47.42</t>
+          <t>47.28</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>146516831.0</t>
+          <t>111884228.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>86052402.7</t>
+          <t>83731647.22</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>65702790</v>
+        <v>45580107</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>46.82</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.42</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>216518198.4</t>
+          <t>146516831.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>85485799.7</t>
+          <t>86052402.7</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>82378616</v>
+        <v>65702790</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>211755874.2</t>
+          <t>216518198.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>84907732.44</t>
+          <t>85485799.7</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>199250041</v>
+        <v>82378616</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>47.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>47.67</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>188514316.2</t>
+          <t>211755874.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>82208595.36</t>
+          <t>84907732.44</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>166509589</v>
+        <v>199250041</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8624,17 +8624,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.22</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>165887158.6</t>
+          <t>188514316.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>79329370.94</t>
+          <t>82208595.36</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>218743119</v>
+        <v>166509589</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>131266427.6</t>
+          <t>165887158.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>75737222.34</t>
+          <t>79329370.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>415709627</v>
+        <v>218743119</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-18.78</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,57 +9734,57 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,19 +9794,19 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>70786468.4</t>
+          <t>131266427.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>67919282.7</t>
+          <t>75737222.34</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3637077.537691697</t>
+          <t>22884307.44448899</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>58566995</v>
+        <v>415709627</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1708.183</t>
+          <t>1201.424</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-17.35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,68 +10149,68 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>754</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.17999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -10220,27 +10220,27 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.04</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.71</t>
+          <t>-25.04</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-83.07</t>
+          <t>-84.07</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>157142243.269341</t>
+          <t>156984672.416309</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>83042251.0</t>
+          <t>58566995.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>69130629.0</t>
+          <t>70786468.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>64051334.6</t>
+          <t>61990972.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>67435324.36</t>
+          <t>67919282.7</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>5079294</t>
+          <t>8795496</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1558433.170673689</t>
+          <t>-1878224.611753383</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3129592.743032247</t>
+          <t>-3637077.537691697</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>83042251</v>
+        <v>58566995</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>48.25</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>31.99</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>31.38</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31.62</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>436235108.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>163075735.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>163075735</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>120542346.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>106027794.62</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>106027794.62</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>23813420.93522564</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>436235108</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>436235108.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.4</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>31.27</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>31.61</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>31.61</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>74194978.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>90018253.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>90018253.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>85751812.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>101483765.1</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>101483765.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1753824.401134402</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>74194978</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>74194978.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>31.63</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>31.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>160381912.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>98740967.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>98740967.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>92145190.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>104398068.18</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>104398068.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>574189.9183917642</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>160381912</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>30.85</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>31.21</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>31.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>92683555.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>82943757.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>82943757.40000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>93041524.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>110958961.04</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>110958961.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-5354896.479370564</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>92683555</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>92683555.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>30.83</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>31.2</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>51883122.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>76714098.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>76714098.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>116606296.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>127513369.12</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>127513369.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-6380378.209053501</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>51883122</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>51883122.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>30.95</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>31.23</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>70947702.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>78008957.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>78008957.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>135866087.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>132601320.34</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>132601320.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-3246006.493991509</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>70947702</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>70947702.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>31.21</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>117808545.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>81485371.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>81485371</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>134782845.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>133719606.02</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>133719606.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-695037.3834032714</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>117808545</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>117808545.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>31.38</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>31.28</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>31.82</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>31.28</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.82</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>81395863.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>85549414.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>85549414.40000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>131413112.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>134538953.8</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>134538953.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-2046777.640298501</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>81395863</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>81395863.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>31.76</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>31.85</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>61535262.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>103139291.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>103139291</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>128774154.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>137249141.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>137249141.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-3377.162995308638</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>61535262</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>61535262.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>31.96</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>31.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>31.87</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>31.87</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>58357415.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>156498494.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>156498494.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>129085113.6</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>141953833.54</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>141953833.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>5043808.524687648</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>58357415</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>58357415.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>31.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>88329770.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>193723218.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>193723218.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>128668962.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>147438804.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>147438804.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>12414421.38121018</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>88329770</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>88329770.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>41.23</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>46.87</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>46.87</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>31333478.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>46398517.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>46398517.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>131458358.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>82367727.08</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>82367727.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-12563936.95104639</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>31333478</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>31333478.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>41.15</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>45.63</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>46.99</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>45.63</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>46.99</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>36693061.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>56607545.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>56607545.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>134181709.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>82624485.32</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>82624485.31999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-9404152.255840585</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>36693061</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>36693061.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>40.98999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>47.13</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>47.13</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>52683153.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>89118941.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>89118941.40000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>138816628.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>83437284.84</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>83437284.84</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-5128552.57498084</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>52683153</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>52683153.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>41.09</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>47.28</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>46.37</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>47.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>45580107.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>111884228.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>111884228.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>138885693.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>83731647.22</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>83731647.22</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-550614.5817890316</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>45580107</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>45580107.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>41.45</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>46.82</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>47.42</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>46.82</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>47.42</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>65702790.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>146516831.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>146516831</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>138891629.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>86052402.7</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>86052402.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>6770002.28640601</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>65702790</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>65702790.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>42.15</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>47.27</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.55</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.55</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>82378616.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>216518198.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>216518198.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>143652333.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>85485799.7</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>85485799.7</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>14830238.83788446</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>82378616</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>82378616.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>43.67</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>47.72</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.67</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.67</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>199250041.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>211755874.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>211755874.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>140443251.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>84907732.44</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>84907732.44</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>24028515.4529292</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>199250041</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>199250041.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>45.36</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>48.22</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>47.82</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>47.82</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>166509589.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>188514316.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>188514316.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>128881598.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>82208595.36</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>82208595.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>23788810.95824565</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>166509589</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>166509589.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>46.89</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>48.6</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>47.92</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>47.92</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>218743119.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>165887158.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>165887158.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>115754398.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>79329370.94</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>79329370.94</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>26104681.14590324</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>218743119</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>218743119.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>48.22000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>48.9</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>48.0</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>48</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>415709627.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>131266427.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>131266427.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>98323015.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>75737222.34</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>75737222.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>22884307.44448899</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>415709627</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>415709627.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>49.17999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.1</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>48.04</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>48.04</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>58566995.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>70786468.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>70786468.40000001</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>61990972.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>67919282.7</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>67919282.7</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-3637077.537691697</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>58566995</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>58566995.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13021.446</t>
+          <t>5223.804</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>31.38</v>
+        <v>31.51</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.62</v>
+        <v>31.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5869.38</t>
+          <t>380.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.76</t>
+          <t>-95.09</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>163075735</v>
+        <v>187748457.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>120542346.2</t>
+          <t>132231278.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>106027794.62</v>
+        <v>106997605.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>42533388</t>
+          <t>55517179</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3279487.95126148</t>
+          <t>6088955.842959256</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>23813420.93522564</t>
+          <t>21541029.24729702</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2321.952</t>
+          <t>13021.446</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>31.27</v>
+        <v>31.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.61</v>
+        <v>31.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>5869.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-99.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>90018253.8</v>
+        <v>163075735</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>85751812.4</t>
+          <t>120542346.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>101483765.1</v>
+        <v>106027794.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4266441</t>
+          <t>42533388</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-453954.409459276</t>
+          <t>3279487.95126148</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1753824.401134402</t>
+          <t>23813420.93522564</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>98740967.2</v>
+        <v>90018253.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>104398068.18</v>
+        <v>101483765.1</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,209 +2304,209 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>190499604.0214592</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>98740967.2</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>104398068.18</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>28.15</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>13.68</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>190395921.3567335</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>82943757.40000001</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>110958961.04</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.2</v>
+        <v>31.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.73</v>
+        <v>31.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>76714098.8</v>
+        <v>82943757.40000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>127513369.12</v>
+        <v>110958961.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,63 +3164,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.23</v>
+        <v>31.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.77</v>
+        <v>31.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>78008957.40000001</v>
+        <v>76714098.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>132601320.34</v>
+        <v>127513369.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,69 +3478,69 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8.93</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.26</v>
+        <v>31.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>81485371</v>
+        <v>78008957.40000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>133719606.02</v>
+        <v>132601320.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>9.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.28</v>
+        <v>31.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.82</v>
+        <v>31.8</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>85549414.40000001</v>
+        <v>81485371</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>134538953.8</v>
+        <v>133719606.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.3</v>
+        <v>31.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>261.70</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.04</t>
+          <t>-101.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>61535262.0</t>
+          <t>81395863.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>103139291</v>
+        <v>85549414.40000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>128774154.3</t>
+          <t>131413112.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>137249141.86</v>
+        <v>134538953.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-25634863</t>
+          <t>-45863697</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4326339.40180349</t>
+          <t>3345859.856864722</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3377.162995308638</t>
+          <t>-2046777.640298501</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>61535262.0</t>
+          <t>81395863.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>6.99</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>31.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>156498494.4</v>
+        <v>103139291</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>141953833.54</v>
+        <v>137249141.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5043808.524687648</t>
+          <t>-3377.162995308638</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2767.799</t>
+          <t>1840.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50.56</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>62.26</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>61.64</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.26</v>
+        <v>31.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.85</v>
+        <v>31.87</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>187.70</t>
+          <t>256.32</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.53</t>
+          <t>-103.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190395921.3567335</t>
+          <t>190499604.0214592</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>193723218.2</v>
+        <v>156498494.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>128668962.4</t>
+          <t>129085113.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>147438804.66</v>
+        <v>141953833.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>65054255</t>
+          <t>27413380</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5126242.79007884</t>
+          <t>5113560.595403272</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>12414421.38121018</t>
+          <t>5043808.524687648</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>88329770.0</t>
+          <t>58357415.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>12.43</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>104.84</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29988</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.05</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN15" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN16" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN17" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8946,17 +8946,17 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>48.6</v>
+        <v>48.22</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.92</v>
+        <v>47.82</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>165887158.6</v>
+        <v>188514316.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>79329370.94</v>
+        <v>82208595.36</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="AN22" t="n">
-        <v>48</v>
+        <v>47.92</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>131266427.6</v>
+        <v>165887158.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>75737222.34</v>
+        <v>79329370.94</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1201.424</t>
+          <t>9151.696</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-17.35</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-6.85</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,54 +10044,54 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>495</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.17999999999999</t>
+          <t>48.22000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="AN23" t="n">
-        <v>48.04</v>
+        <v>48</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,19 +10100,19 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-25.04</t>
+          <t>-127.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>0.27</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-84.07</t>
+          <t>-87.93</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>156984672.416309</t>
+          <t>156804507.8657143</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>70786468.40000001</v>
+        <v>131266427.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>61990972.2</t>
+          <t>98323015.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>67919282.7</v>
+        <v>75737222.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8795496</t>
+          <t>32943412</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1878224.611753383</t>
+          <t>1931395.704591597</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3637077.537691697</t>
+          <t>22884307.44448899</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>58566995.0</t>
+          <t>415709627.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.37</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>30453</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>48.25</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5223.804</t>
+          <t>3019.217</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>39.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,94 +993,94 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="AN2" t="n">
         <v>31.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>380.65</t>
+          <t>200.53</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.09</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>187748457.8</v>
+        <v>189357276.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>132231278.3</t>
+          <t>136150516.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>106997605.88</v>
+        <v>106966747.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>55517179</t>
+          <t>53206759</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>6088955.842959256</t>
+          <t>7278793.045513918</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>21541029.24729702</t>
+          <t>13822897.65956455</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13021.446</t>
+          <t>5223.804</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>31.38</v>
+        <v>31.51</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.62</v>
+        <v>31.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5869.38</t>
+          <t>380.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.76</t>
+          <t>-95.09</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>163075735</v>
+        <v>187748457.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>120542346.2</t>
+          <t>132231278.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>106027794.62</v>
+        <v>106997605.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>42533388</t>
+          <t>55517179</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3279487.95126148</t>
+          <t>6088955.842959256</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>23813420.93522564</t>
+          <t>21541029.24729702</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2321.952</t>
+          <t>13021.446</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.27</v>
+        <v>31.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.61</v>
+        <v>31.62</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>5869.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-99.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>90018253.8</v>
+        <v>163075735</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>85751812.4</t>
+          <t>120542346.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>101483765.1</v>
+        <v>106027794.62</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4266441</t>
+          <t>42533388</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-453954.409459276</t>
+          <t>3279487.95126148</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1753824.401134402</t>
+          <t>23813420.93522564</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>98740967.2</v>
+        <v>90018253.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>104398068.18</v>
+        <v>101483765.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>13.68</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,209 +2734,209 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>190443306.6878572</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>98740967.2</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>104398068.18</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>190499604.0214592</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>82943757.40000001</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>110958961.04</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>28.15</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/07/23</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>11.37</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.2</v>
+        <v>31.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.73</v>
+        <v>31.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>76714098.8</v>
+        <v>82943757.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>127513369.12</v>
+        <v>110958961.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>10.30</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,63 +3594,63 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.23</v>
+        <v>31.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.77</v>
+        <v>31.73</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>78008957.40000001</v>
+        <v>76714098.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>132601320.34</v>
+        <v>127513369.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>8.70</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,69 +3908,69 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>9.23</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.26</v>
+        <v>31.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>81485371</v>
+        <v>78008957.40000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>133719606.02</v>
+        <v>132601320.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.28</v>
+        <v>31.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.82</v>
+        <v>31.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>85549414.40000001</v>
+        <v>81485371</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>134538953.8</v>
+        <v>133719606.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.3</v>
+        <v>31.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>261.70</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.04</t>
+          <t>-101.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>61535262.0</t>
+          <t>81395863.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>103139291</v>
+        <v>85549414.40000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>128774154.3</t>
+          <t>131413112.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>137249141.86</v>
+        <v>134538953.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-25634863</t>
+          <t>-45863697</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4326339.40180349</t>
+          <t>3345859.856864722</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-3377.162995308638</t>
+          <t>-2046777.640298501</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>61535262.0</t>
+          <t>81395863.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1840.4</t>
+          <t>1952.908</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>62.26</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>61.64</t>
+          <t>60.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>31.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.87</v>
+        <v>31.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>256.32</t>
+          <t>261.70</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.37</t>
+          <t>-102.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190499604.0214592</t>
+          <t>190443306.6878572</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>156498494.4</v>
+        <v>103139291</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>129085113.6</t>
+          <t>128774154.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>141953833.54</v>
+        <v>137249141.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>27413380</t>
+          <t>-25634863</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>5113560.595403272</t>
+          <t>4326339.40180349</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5043808.524687648</t>
+          <t>-3377.162995308638</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>58357415.0</t>
+          <t>61535262.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.38</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>36.06</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29988</t>
+          <t>29809</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,68 +6609,68 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,68 +7039,68 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN16" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN17" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>48.6</v>
+        <v>48.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.92</v>
+        <v>47.82</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>165887158.6</v>
+        <v>188514316.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>79329370.94</v>
+        <v>82208595.36</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9151.696</t>
+          <t>5016.444</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.85</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>54.81</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-3.50</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>10.71</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-8.51</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>48.22000000000001</t>
+          <t>46.89</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="AN23" t="n">
-        <v>48</v>
+        <v>47.92</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>47.08</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-127.98</t>
+          <t>-524.68</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-94.78</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>156804507.8657143</t>
+          <t>156681415.8937232</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>131266427.6</v>
+        <v>165887158.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>98323015.2</t>
+          <t>115754398.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>75737222.34</v>
+        <v>79329370.94</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>32943412</t>
+          <t>50132760</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1931395.704591597</t>
+          <t>5650362.69556262</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>22884307.44448899</t>
+          <t>26104681.14590324</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>415709627.0</t>
+          <t>218743119.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.36</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30307</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>47.75</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3019.217</t>
+          <t>3667.38</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,154 +933,154 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.55</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>93.41</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>31.66</v>
+        <v>31.8</v>
       </c>
       <c r="AN2" t="n">
         <v>31.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>200.53</t>
+          <t>127.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-85.56</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>100727647.0</t>
+          <t>122801691.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>189357276.2</v>
+        <v>181841232</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>136150516.8</t>
+          <t>140291099.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>106966747.68</v>
+        <v>107174018.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>53206759</t>
+          <t>41550132</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>7278793.045513918</t>
+          <t>7655930.485690653</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>13822897.65956455</t>
+          <t>9730186.406662703</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>100727647.0</t>
+          <t>122801691.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5223.804</t>
+          <t>3019.217</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>39.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1363,49 +1363,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1413,104 +1413,104 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.55</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="AN3" t="n">
         <v>31.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>380.65</t>
+          <t>200.53</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.09</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>187748457.8</v>
+        <v>189357276.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>132231278.3</t>
+          <t>136150516.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>106997605.88</v>
+        <v>106966747.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>55517179</t>
+          <t>53206759</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>6088955.842959256</t>
+          <t>7278793.045513918</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>21541029.24729702</t>
+          <t>13822897.65956455</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13021.446</t>
+          <t>5223.804</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1793,49 +1793,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1843,27 +1843,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.38</v>
+        <v>31.51</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.62</v>
+        <v>31.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>5869.38</t>
+          <t>380.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.76</t>
+          <t>-95.09</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>163075735</v>
+        <v>187748457.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>120542346.2</t>
+          <t>132231278.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>106027794.62</v>
+        <v>106997605.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>42533388</t>
+          <t>55517179</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3279487.95126148</t>
+          <t>6088955.842959256</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>23813420.93522564</t>
+          <t>21541029.24729702</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2321.952</t>
+          <t>13021.446</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2223,49 +2223,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2273,27 +2273,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.27</v>
+        <v>31.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.61</v>
+        <v>31.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>5869.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-99.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>90018253.8</v>
+        <v>163075735</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>85751812.4</t>
+          <t>120542346.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>101483765.1</v>
+        <v>106027794.62</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4266441</t>
+          <t>42533388</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-453954.409459276</t>
+          <t>3279487.95126148</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1753824.401134402</t>
+          <t>23813420.93522564</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2653,49 +2653,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,27 +2703,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>98740967.2</v>
+        <v>90018253.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>104398068.18</v>
+        <v>101483765.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3083,49 +3083,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,27 +3133,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,209 +3164,209 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>190434404.0199715</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>98740967.2</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>104398068.18</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>190443306.6878572</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>82943757.40000001</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>110958961.04</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-6.14</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3513,49 +3513,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.2</v>
+        <v>31.21</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.73</v>
+        <v>31.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>76714098.8</v>
+        <v>82943757.40000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>127513369.12</v>
+        <v>110958961.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3943,49 +3943,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3993,27 +3993,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,63 +4024,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.23</v>
+        <v>31.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.77</v>
+        <v>31.73</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>78008957.40000001</v>
+        <v>76714098.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>132601320.34</v>
+        <v>127513369.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,84 +4338,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7.83</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8.68</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4423,27 +4423,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.26</v>
+        <v>31.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>81485371</v>
+        <v>78008957.40000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>133719606.02</v>
+        <v>132601320.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4803,49 +4803,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,27 +4853,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.28</v>
+        <v>31.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.82</v>
+        <v>31.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>85549414.40000001</v>
+        <v>81485371</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>134538953.8</v>
+        <v>133719606.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1952.908</t>
+          <t>2631.169</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-34.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,49 +5233,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-10-28 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-10-31 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5283,27 +5283,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,68 +5314,68 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.38</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.38</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.3</v>
+        <v>31.28</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.85</v>
+        <v>31.82</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>261.70</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.04</t>
+          <t>-101.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190443306.6878572</t>
+          <t>190434404.0199715</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>61535262.0</t>
+          <t>81395863.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>103139291</v>
+        <v>85549414.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>128774154.3</t>
+          <t>131413112.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>137249141.86</v>
+        <v>134538953.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-25634863</t>
+          <t>-45863697</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4326339.40180349</t>
+          <t>3345859.856864722</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3377.162995308638</t>
+          <t>-2046777.640298501</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>61535262.0</t>
+          <t>81395863.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-7.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>104.38</t>
+          <t>103.75</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>36.06</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1130.918</t>
+          <t>1347.469</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-49.63</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>44.65</v>
+        <v>44.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.66</v>
+        <v>46.56</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-173.49</t>
+          <t>-175.31</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>37660141.4</v>
+        <v>38245237.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>74772185.0</t>
+          <t>63682089.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>81458753.88</v>
+        <v>81578099.64</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-37112043</t>
+          <t>-25436852</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3026572.764576255</t>
+          <t>-4630586.329104355</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-14797142.43507398</t>
+          <t>-13452660.9340089</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN17" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8156,12 +8156,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5016.444</t>
+          <t>3978.022</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>54.81</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-3.50</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-8.51</t>
+          <t>-8.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>45.36</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.6</v>
+        <v>48.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>47.92</v>
+        <v>47.82</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-524.68</t>
+          <t>-922.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-94.78</t>
+          <t>-103.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>156681415.8937232</t>
+          <t>156577044.8568376</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>165887158.6</v>
+        <v>188514316.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>115754398.3</t>
+          <t>128881598.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>79329370.94</v>
+        <v>82208595.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>50132760</t>
+          <t>59632717</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>5650362.69556262</t>
+          <t>8440893.197513856</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>26104681.14590324</t>
+          <t>23788810.95824565</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>218743119.0</t>
+          <t>166509589.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.36</t>
+          <t>17.18</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3667.38</t>
+          <t>7512.533</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>33.2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>33.2</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>31.55</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,38 +993,38 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,254 +1034,254 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>33.62</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>31.8</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>108.82</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-80.16</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>190709954.8803419</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>255914072.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>218185050.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>154101652.3</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>109271871.24</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>64083398</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>9032781.5562713</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>16605462.44446486</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>255914072.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5.83</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>107.34</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>36.24</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>30657</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>33.35</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>127.29</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-85.56</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>190434404.0199715</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>122801691.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>181841232</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>140291099.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>107174018.08</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>41550132</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>7655930.485690653</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>9730186.406662703</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>122801691.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>6.04</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>103.75</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>35.92</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>29631</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3019.217</t>
+          <t>3667.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,27 +1338,27 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,94 +1423,94 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.55</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>93.41</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>31.66</v>
+        <v>31.8</v>
       </c>
       <c r="AN3" t="n">
         <v>31.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>200.53</t>
+          <t>127.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-85.56</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>100727647.0</t>
+          <t>122801691.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>189357276.2</v>
+        <v>181841232</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>136150516.8</t>
+          <t>140291099.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>106966747.68</v>
+        <v>107174018.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>53206759</t>
+          <t>41550132</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>7278793.045513918</t>
+          <t>7655930.485690653</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13822897.65956455</t>
+          <t>9730186.406662703</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>100727647.0</t>
+          <t>122801691.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5223.804</t>
+          <t>3019.217</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>39.08</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,94 +1853,94 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.55</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="AN4" t="n">
         <v>31.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>380.65</t>
+          <t>200.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.09</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>187748457.8</v>
+        <v>189357276.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>132231278.3</t>
+          <t>136150516.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>106997605.88</v>
+        <v>106966747.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>55517179</t>
+          <t>53206759</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6088955.842959256</t>
+          <t>7278793.045513918</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>21541029.24729702</t>
+          <t>13822897.65956455</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13021.446</t>
+          <t>5223.804</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,102 +2198,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>8.85</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>0.63</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>35.29</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>8.85</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14.30</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>3.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.38</v>
+        <v>31.51</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.62</v>
+        <v>31.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5869.38</t>
+          <t>380.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-99.76</t>
+          <t>-95.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>163075735</v>
+        <v>187748457.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>120542346.2</t>
+          <t>132231278.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>106027794.62</v>
+        <v>106997605.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>42533388</t>
+          <t>55517179</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3279487.95126148</t>
+          <t>6088955.842959256</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>23813420.93522564</t>
+          <t>21541029.24729702</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2321.952</t>
+          <t>13021.446</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.27</v>
+        <v>31.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.61</v>
+        <v>31.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>5869.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-99.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>90018253.8</v>
+        <v>163075735</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>85751812.4</t>
+          <t>120542346.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>101483765.1</v>
+        <v>106027794.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4266441</t>
+          <t>42533388</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-453954.409459276</t>
+          <t>3279487.95126148</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1753824.401134402</t>
+          <t>23813420.93522564</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>98740967.2</v>
+        <v>90018253.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>104398068.18</v>
+        <v>101483765.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3446,14 +3446,14 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,209 +3594,209 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>190709954.8803419</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>98740967.2</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>104398068.18</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>190434404.0199715</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>82943757.40000001</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>110958961.04</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-6.14</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.58</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.83</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.2</v>
+        <v>31.21</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.73</v>
+        <v>31.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>31.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-80.54</t>
+          <t>-30.97</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.94</t>
+          <t>-105.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>76714098.8</v>
+        <v>82943757.40000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>116606296.6</t>
+          <t>93041524.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>127513369.12</v>
+        <v>110958961.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-39892197</t>
+          <t>-10097766</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>546297.100938415</t>
+          <t>-361578.8344937356</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-6380378.209053501</t>
+          <t>-5354896.479370564</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>51883122.0</t>
+          <t>92683555.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2321.61</t>
+          <t>1669.106</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.58</t>
+          <t>-34.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>25.58</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>10.08</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.23</v>
+        <v>31.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.77</v>
+        <v>31.73</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-129.99</t>
+          <t>-80.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.94</t>
+          <t>-104.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>78008957.40000001</v>
+        <v>76714098.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>135866087.8</t>
+          <t>116606296.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>132601320.34</v>
+        <v>127513369.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-57857130</t>
+          <t>-39892197</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1805692.611846036</t>
+          <t>546297.100938415</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3246006.493991509</t>
+          <t>-6380378.209053501</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>70947702.0</t>
+          <t>51883122.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3884.372</t>
+          <t>2321.61</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,84 +4768,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>30.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10.92</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-42.58</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>33.2</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>8.13</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-39.54</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>31.55</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.26</v>
+        <v>31.23</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.8</v>
+        <v>31.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>31.47</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-122.29</t>
+          <t>-129.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.66</t>
+          <t>-103.94</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>81485371</v>
+        <v>78008957.40000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>134782845.5</t>
+          <t>135866087.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>133719606.02</v>
+        <v>132601320.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-53297474</t>
+          <t>-57857130</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2724183.358361954</t>
+          <t>1805692.611846036</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-695037.3834032714</t>
+          <t>-3246006.493991509</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>117808545.0</t>
+          <t>70947702.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.68</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2631.169</t>
+          <t>3884.372</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>31.21</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.28</v>
+        <v>31.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.82</v>
+        <v>31.8</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>-122.29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.85</t>
+          <t>-102.66</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>190434404.0199715</t>
+          <t>190709954.8803419</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>85549414.40000001</v>
+        <v>81485371</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>131413112.1</t>
+          <t>134782845.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>134538953.8</v>
+        <v>133719606.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-45863697</t>
+          <t>-53297474</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3345859.856864722</t>
+          <t>2724183.358361954</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-2046777.640298501</t>
+          <t>-695037.3834032714</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>81395863.0</t>
+          <t>117808545.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-8.68</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>103.75</t>
+          <t>107.34</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>36.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>30657</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1347.469</t>
+          <t>574.591</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-39.94</t>
+          <t>-22.74</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.75</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14.72</t>
+          <t>6.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,42 +5744,42 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>31.27</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.60</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5788,29 +5788,29 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>44.27</v>
+        <v>43.87</v>
       </c>
       <c r="AN13" t="n">
-        <v>46.56</v>
+        <v>46.46</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>46.62</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-175.31</t>
+          <t>-176.43</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>38245237.2</v>
+        <v>35633146.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>63682089.3</t>
+          <t>46120346.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>81578099.64</v>
+        <v>81185268.44</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-25436852</t>
+          <t>-10487199</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4630586.329104355</t>
+          <t>-6160251.379998012</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-13452660.9340089</t>
+          <t>-14573409.15991313</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>55608632.0</t>
+          <t>23632608.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1130.918</t>
+          <t>1347.469</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-49.63</t>
+          <t>-39.94</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-14.75</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.72</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-7.32</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>44.65</v>
+        <v>44.27</v>
       </c>
       <c r="AN14" t="n">
-        <v>46.66</v>
+        <v>46.56</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.72</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-14.01</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-173.49</t>
+          <t>-175.31</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>37660141.4</v>
+        <v>38245237.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>74772185.0</t>
+          <t>63682089.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>81458753.88</v>
+        <v>81578099.64</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-37112043</t>
+          <t>-25436852</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3026572.764576255</t>
+          <t>-4630586.329104355</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-14797142.43507398</t>
+          <t>-13452660.9340089</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>47011357.0</t>
+          <t>55608632.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>495.163</t>
+          <t>1130.918</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-59.35</t>
+          <t>-49.63</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-8.20</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>44.99</v>
+        <v>44.65</v>
       </c>
       <c r="AN15" t="n">
-        <v>46.76</v>
+        <v>46.66</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>46.72</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-21.39</t>
+          <t>-14.01</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-170.91</t>
+          <t>-173.49</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>37373891.4</v>
+        <v>37660141.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>91945361.2</t>
+          <t>74772185.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>81397712.23999999</v>
+        <v>81458753.88</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-54571469</t>
+          <t>-37112043</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-886469.1881221232</t>
+          <t>-3026572.764576255</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-15268224.31391429</t>
+          <t>-14797142.43507398</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>20579658.0</t>
+          <t>47011357.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>754.379</t>
+          <t>495.163</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-64.70</t>
+          <t>-59.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-13.40</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>48.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-8.20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>45.3</v>
+        <v>44.99</v>
       </c>
       <c r="AN16" t="n">
-        <v>46.87</v>
+        <v>46.76</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.78</t>
+          <t>46.76</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-21.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-167.12</t>
+          <t>-170.91</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>46398517.8</v>
+        <v>37373891.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>131458358.1</t>
+          <t>91945361.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>82367727.08</v>
+        <v>81397712.23999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-85059840</t>
+          <t>-54571469</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1728395.380203726</t>
+          <t>-886469.1881221232</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-12563936.95104639</t>
+          <t>-15268224.31391429</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>31333478.0</t>
+          <t>20579658.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>894.804</t>
+          <t>754.379</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-57.81</t>
+          <t>-64.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.85</t>
+          <t>-13.81</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>8.24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>48.15</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>45.63</v>
+        <v>45.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>46.99</v>
+        <v>46.87</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.81</t>
+          <t>46.78</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-32.08</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-161.74</t>
+          <t>-167.12</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>56607545.4</v>
+        <v>46398517.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>134181709.8</t>
+          <t>131458358.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>82624485.31999999</v>
+        <v>82367727.08</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-77574164</t>
+          <t>-85059840</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>4327001.258612839</t>
+          <t>1728395.380203726</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-9404152.255840585</t>
+          <t>-12563936.95104639</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>36693061.0</t>
+          <t>31333478.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-9.49</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1280.793</t>
+          <t>894.804</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-35.80</t>
+          <t>-57.81</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.43</t>
+          <t>-14.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>11.64</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.98999999999999</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>45.99</v>
+        <v>45.63</v>
       </c>
       <c r="AN18" t="n">
-        <v>47.13</v>
+        <v>46.99</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>46.81</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-60.10</t>
+          <t>-45.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-154.73</t>
+          <t>-161.74</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>89118941.40000001</v>
+        <v>56607545.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>138816628.8</t>
+          <t>134181709.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>83437284.84</v>
+        <v>82624485.31999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-49697687</t>
+          <t>-77574164</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>6823574.624877097</t>
+          <t>4327001.258612839</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-5128552.57498084</t>
+          <t>-9404152.255840585</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>52683153.0</t>
+          <t>36693061.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-9.05</t>
+          <t>-9.49</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.55</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1105.216</t>
+          <t>1280.793</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-19.44</t>
+          <t>-35.80</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.43</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>13.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>10.93</t>
+          <t>11.64</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-11.39</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>40.98999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>46.37</v>
+        <v>45.99</v>
       </c>
       <c r="AN19" t="n">
-        <v>47.28</v>
+        <v>47.13</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>46.84</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-60.10</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-146.51</t>
+          <t>-154.73</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>111884228.6</v>
+        <v>89118941.40000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>138885693.6</t>
+          <t>138816628.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>83731647.22</v>
+        <v>83437284.84</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-27001465</t>
+          <t>-49697687</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>8996688.661214905</t>
+          <t>6823574.624877097</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-550614.5817890316</t>
+          <t>-5128552.57498084</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>45580107.0</t>
+          <t>52683153.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-9.05</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1580.018</t>
+          <t>1105.216</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>-19.44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>12.08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>10.93</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-11.48</t>
+          <t>-11.39</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.09</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>46.82</v>
+        <v>46.37</v>
       </c>
       <c r="AN20" t="n">
-        <v>47.42</v>
+        <v>47.28</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>46.88</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-113.18</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-137.01</t>
+          <t>-146.51</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>146516831</v>
+        <v>111884228.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>138891629.3</t>
+          <t>138885693.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>86052402.7</v>
+        <v>83731647.22</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7625201</t>
+          <t>-27001465</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>10732561.97812471</t>
+          <t>8996688.661214905</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>6770002.28640601</t>
+          <t>-550614.5817890316</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>65702790.0</t>
+          <t>45580107.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2004.589</t>
+          <t>1580.018</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>50.72</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.12</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21.90</t>
+          <t>17.26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-10.83</t>
+          <t>-11.48</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>47.27</v>
+        <v>46.82</v>
       </c>
       <c r="AN21" t="n">
-        <v>47.55</v>
+        <v>47.42</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>46.94</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-170.08</t>
+          <t>-113.18</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-126.53</t>
+          <t>-137.01</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>216518198.4</v>
+        <v>146516831</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>143652333.4</t>
+          <t>138891629.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>85485799.7</v>
+        <v>86052402.7</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>72865865</t>
+          <t>7625201</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>11453027.37661902</t>
+          <t>10732561.97812471</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>14830238.83788446</t>
+          <t>6770002.28640601</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>82378616.0</t>
+          <t>65702790.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-9.27</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4904.003</t>
+          <t>2004.589</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>50.78</t>
+          <t>50.72</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>53.58</t>
+          <t>21.90</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-10.83</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>47.72</v>
+        <v>47.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>47.67</v>
+        <v>47.55</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>46.94</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-295.26</t>
+          <t>-170.08</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.25</t>
+          <t>-126.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>211755874.2</v>
+        <v>216518198.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>140443251.6</t>
+          <t>143652333.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>84907732.44</v>
+        <v>85485799.7</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>71312622</t>
+          <t>72865865</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>10838988.92911622</t>
+          <t>11453027.37661902</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>24028515.4529292</t>
+          <t>14830238.83788446</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>199250041.0</t>
+          <t>82378616.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-11.26</t>
+          <t>-9.27</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3978.022</t>
+          <t>4904.003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>50.78</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.40</t>
+          <t>-16.51</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>53.58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>575</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-8.07</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>48.22</v>
+        <v>47.72</v>
       </c>
       <c r="AN23" t="n">
-        <v>47.82</v>
+        <v>47.67</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-922.98</t>
+          <t>-295.26</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-103.99</t>
+          <t>-115.25</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>156577044.8568376</t>
+          <t>156404743.1031294</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>188514316.2</v>
+        <v>211755874.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>128881598.6</t>
+          <t>140443251.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>82208595.36</v>
+        <v>84907732.44</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>59632717</t>
+          <t>71312622</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>8440893.197513856</t>
+          <t>10838988.92911622</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>23788810.95824565</t>
+          <t>24028515.4529292</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>166509589.0</t>
+          <t>199250041.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-11.26</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>29942</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.65</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/營造設置.xlsx
+++ b/Result/checksun_type/營造設置.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7512.533</t>
+          <t>8234.331</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,33 +993,33 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.41</t>
+          <t>95.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>32.02</v>
+        <v>32.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.66</v>
+        <v>31.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>108.82</t>
+          <t>99.62</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-73.58</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>190709954.8803419</t>
+          <t>191054391.0384068</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>255914072.0</t>
+          <t>288565716.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>218185050.8</v>
+        <v>188651172.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>154101652.3</t>
+          <t>175863453.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>109271871.24</v>
+        <v>113163621.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>64083398</t>
+          <t>12787718</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>9032781.5562713</t>
+          <t>11251106.3029703</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>16605462.44446486</t>
+          <t>23451892.40981477</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>255914072.0</t>
+          <t>288565716.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3667.38</t>
+          <t>7512.533</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,74 +1328,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>33.2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>29.62</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-12-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>33.2</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>33.2</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>31.55</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,38 +1423,38 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,254 +1464,254 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>33.62</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>31.8</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>108.82</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-80.16</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>191054391.0384068</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>255914072.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>218185050.8</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>154101652.3</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>109271871.24</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>64083398</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>9032781.5562713</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>16605462.44446486</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>255914072.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>5.68</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>23.80</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>110.16</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>36.17</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>31460</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>中鼎-其他-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他右下上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>33.35</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>34.45</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>127.29</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-85.56</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>190709954.8803419</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>122801691.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>181841232</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>140291099.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>107174018.08</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>41550132</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>7655930.485690653</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>9730186.406662703</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>122801691.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>5.83</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>23.80</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>107.34</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>9.28%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>7.16%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>36.24</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>30657</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>工程服務92.21%、環境資源服務7.35%、一般銷售0.41%、其他0.03% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>中鼎-其他-上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>其他右下上市</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3019.217</t>
+          <t>3667.38</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,94 +1853,94 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>93.55</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>97.85</t>
+          <t>93.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.66</v>
+        <v>31.8</v>
       </c>
       <c r="AN4" t="n">
         <v>31.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>200.53</t>
+          <t>127.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-90.15</t>
+          <t>-85.56</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>190709954.8803419</t>
+          <t>191054391.0384068</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>100727647.0</t>
+          <t>122801691.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>189357276.2</v>
+        <v>181841232</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>136150516.8</t>
+          <t>140291099.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>106966747.68</v>
+        <v>107174018.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>53206759</t>
+          <t>41550132</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>7278793.045513918</t>
+          <t>7655930.485690653</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>13822897.65956455</t>
+          <t>9730186.406662703</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>100727647.0</t>
+          <t>122801691.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5223.804</t>
+          <t>3019.217</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>39.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,94 +2283,94 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.55</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.85</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.51</v>
+        <v>31.66</v>
       </c>
       <c r="AN5" t="n">
         <v>31.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>31.74</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>380.65</t>
+          <t>200.53</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.09</t>
+          <t>-90.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>190709954.8803419</t>
+          <t>191054391.0384068</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>187748457.8</v>
+        <v>189357276.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>132231278.3</t>
+          <t>136150516.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>106997605.88</v>
+        <v>106966747.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>55517179</t>
+          <t>53206759</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6088955.842959256</t>
+          <t>7278793.045513918</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>21541029.24729702</t>
+          <t>13822897.65956455</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>175246736.0</t>
+          <t>100727647.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13021.446</t>
+          <t>5223.804</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.30</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.38</v>
+        <v>31.51</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.62</v>
+        <v>31.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.74</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>5869.38</t>
+          <t>380.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-99.76</t>
+          <t>-95.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>190709954.8803419</t>
+          <t>191054391.0384068</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>163075735</v>
+        <v>187748457.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>120542346.2</t>
+          <t>132231278.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>106027794.62</v>
+        <v>106997605.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>42533388</t>
+          <t>55517179</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3279487.95126148</t>
+          <t>6088955.842959256</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>23813420.93522564</t>
+          <t>21541029.24729702</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>436235108.0</t>
+          <t>175246736.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2321.952</t>
+          <t>13021.446</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>14.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.99</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.27</v>
+        <v>31.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.61</v>
+        <v>31.62</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>171.12</t>
+          <t>5869.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.25</t>
+          <t>-99.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>190709954.8803419</t>
+          <t>191054391.0384068</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>90018253.8</v>
+        <v>163075735</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>85751812.4</t>
+          <t>120542346.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>101483765.1</v>
+        <v>106027794.62</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4266441</t>
+          <t>42533388</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-453954.409459276</t>
+          <t>3279487.95126148</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1753824.401134402</t>
+          <t>23813420.93522564</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>74194978.0</t>
+          <t>436235108.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>33.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5002.075</t>
+          <t>2321.952</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.24</v>
+        <v>31.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.63</v>
+        <v>31.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>31.61</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>61.33</t>
+          <t>171.12</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.64</t>
+          <t>-103.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>190709954.8803419</t>
+          <t>191054391.0384068</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>98740967.2</v>
+        <v>90018253.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>92145190.8</t>
+          <t>85751812.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>104398068.18</v>
+        <v>101483765.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6595776</t>
+          <t>4266441</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-217614.4109728895</t>
+          <t>-453954.409459276</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>574189.9183917642</t>
+          <t>-1753824.401134402</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>160381912.0</t>
+          <t>74194978.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2963.674</t>
+          <t>5002.075</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,209 +4024,209 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>61.33</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-104.64</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>191054391.0384068</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>98740967.2</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>92145190.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>104398068.18</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6595776</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-217614.4109728895</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>574189.9183917642</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>160381912.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>33.4</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-4.19</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>中鼎</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-26.84197020242426</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-29.45200131802344</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-23.99786452462518</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>31.21</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>31.58</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-30.97</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-105.35</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>190709954.8803419</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>82943757.40000001</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>93041524.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>110958961.04</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-10097766</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-361578.8344937356</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-5354896.479370564</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>92683555.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>33.4</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-6.14</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>中鼎</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-26.84197020242426</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-29.45200131802344</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-23.99786452462518</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>110.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>36.24</t>
+          <t>36.17</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1669.106</t>
+          <t>2963.674</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,